--- a/src/data/Bargaining_Tracker_Candidate_Dataset.xlsx
+++ b/src/data/Bargaining_Tracker_Candidate_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FEBA RACHEL JOHNY\Desktop\SkillSet\E tu\bargaining-tracker\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1F0FF7-1080-4E5C-97AF-24866F426BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C932F9-0E36-4880-A897-53EAC91DC57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="227">
   <si>
     <t>Employer Name</t>
   </si>
@@ -83,9 +83,6 @@
     <t>Christchurch</t>
   </si>
   <si>
-    <t>2026-07-02</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
@@ -104,9 +101,6 @@
     <t>Wellington</t>
   </si>
   <si>
-    <t>2026-07-19</t>
-  </si>
-  <si>
     <t>Mereana Roberts</t>
   </si>
   <si>
@@ -122,9 +116,6 @@
     <t>National</t>
   </si>
   <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
     <t>Theo Martin</t>
   </si>
   <si>
@@ -137,9 +128,6 @@
     <t>Terminal Retail Assist</t>
   </si>
   <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
     <t>Ratified</t>
   </si>
   <si>
@@ -188,9 +176,6 @@
     <t>Metro Cleaning Group</t>
   </si>
   <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
     <t>Josh Patel</t>
   </si>
   <si>
@@ -221,9 +206,6 @@
     <t>Civic Property Services</t>
   </si>
   <si>
-    <t>2026-09-17</t>
-  </si>
-  <si>
     <t>Ruby Thompson</t>
   </si>
   <si>
@@ -284,9 +266,6 @@
     <t>SouthWorks Engineering</t>
   </si>
   <si>
-    <t>2026-07-26</t>
-  </si>
-  <si>
     <t>Moana Te Awa</t>
   </si>
   <si>
@@ -299,9 +278,6 @@
     <t>Pacific Packaging Ltd</t>
   </si>
   <si>
-    <t>2026-08-22</t>
-  </si>
-  <si>
     <t>James Liu</t>
   </si>
   <si>
@@ -377,9 +353,6 @@
     <t>Wellington Community Care</t>
   </si>
   <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
     <t>Nadia Khan</t>
   </si>
   <si>
@@ -407,9 +380,6 @@
     <t>National Lab Services</t>
   </si>
   <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
     <t>Grace Milne</t>
   </si>
   <si>
@@ -455,9 +425,6 @@
     <t>Public &amp; Commercial</t>
   </si>
   <si>
-    <t>2026-06-21</t>
-  </si>
-  <si>
     <t>Tony Williams</t>
   </si>
   <si>
@@ -470,9 +437,6 @@
     <t>Public Services Support Ltd</t>
   </si>
   <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
     <t>Alicia Morgan</t>
   </si>
   <si>
@@ -485,9 +449,6 @@
     <t>Regional Venue Operations</t>
   </si>
   <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
     <t>Daniel Rees</t>
   </si>
   <si>
@@ -500,9 +461,6 @@
     <t>National Events Workforce</t>
   </si>
   <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
     <t>Keita Holmes</t>
   </si>
   <si>
@@ -678,9 +636,6 @@
   </si>
   <si>
     <t>chris.brown@example.com</t>
-  </si>
-  <si>
-    <t>moana.teawa@example.com</t>
   </si>
   <si>
     <t>james.liu@example.com</t>
@@ -1207,7 +1162,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="H2" s="3">
         <v>320</v>
@@ -1229,95 +1184,95 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="2">
+        <v>46368</v>
+      </c>
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
       <c r="G3" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="H3" s="3">
         <v>140</v>
       </c>
       <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46331</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="H4" s="3">
         <v>260</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46613</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="H5" s="3">
         <v>410</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -1325,1018 +1280,1018 @@
       <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>38</v>
+      <c r="D6" s="2">
+        <v>47362</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="H6" s="3">
         <v>95</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="H7" s="3">
         <v>85</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="H8" s="3">
         <v>180</v>
       </c>
       <c r="I8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>55</v>
+      <c r="D9" s="2">
+        <v>46579</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="H9" s="3">
         <v>230</v>
       </c>
       <c r="I9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H10" s="3">
         <v>120</v>
       </c>
       <c r="I10" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>66</v>
+        <v>30</v>
+      </c>
+      <c r="D11" s="2">
+        <v>46376</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="H11" s="3">
         <v>510</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G12" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="H12" s="3">
         <v>70</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="H13" s="3">
         <v>160</v>
       </c>
       <c r="I13" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
         <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="H14" s="3">
         <v>460</v>
       </c>
       <c r="I14" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>87</v>
+      <c r="D15" s="2">
+        <v>46594</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="H15" s="3">
         <v>210</v>
       </c>
       <c r="I15" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>92</v>
+        <v>25</v>
+      </c>
+      <c r="D16" s="2">
+        <v>46621</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="H16" s="3">
         <v>175</v>
       </c>
       <c r="I16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="H17" s="3">
         <v>390</v>
       </c>
       <c r="I17" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G18" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="H18" s="3">
         <v>145</v>
       </c>
       <c r="I18" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F19" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G19" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="H19" s="3">
         <v>620</v>
       </c>
       <c r="I19" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
         <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G20" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="H20" s="3">
         <v>980</v>
       </c>
       <c r="I20" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>118</v>
+        <v>25</v>
+      </c>
+      <c r="D21" s="2">
+        <v>46576</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F21" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="G21" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="H21" s="3">
         <v>340</v>
       </c>
       <c r="I21" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="G22" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="H22" s="3">
         <v>275</v>
       </c>
       <c r="I22" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B23" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>128</v>
+        <v>30</v>
+      </c>
+      <c r="D23" s="2">
+        <v>46659</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F23" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="G23" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H23" s="3">
         <v>540</v>
       </c>
       <c r="I23" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="G24" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="H24" s="3">
         <v>190</v>
       </c>
       <c r="I24" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F25" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="G25" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="H25" s="3">
         <v>430</v>
       </c>
       <c r="I25" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>144</v>
+      <c r="D26" s="2">
+        <v>46319</v>
       </c>
       <c r="E26" t="s">
         <v>14</v>
       </c>
       <c r="F26" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G26" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="H26" s="3">
         <v>220</v>
       </c>
       <c r="I26" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>149</v>
+        <v>25</v>
+      </c>
+      <c r="D27" s="2">
+        <v>46583</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F27" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="G27" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="H27" s="3">
         <v>310</v>
       </c>
       <c r="I27" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B28" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>154</v>
+      <c r="D28" s="2">
+        <v>46626</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F28" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="G28" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="H28" s="3">
         <v>130</v>
       </c>
       <c r="I28" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>159</v>
+        <v>30</v>
+      </c>
+      <c r="D29" s="2">
+        <v>46642</v>
       </c>
       <c r="E29" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F29" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="G29" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="H29" s="3">
         <v>205</v>
       </c>
       <c r="I29" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F30" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="G30" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="H30" s="3">
         <v>155</v>
       </c>
       <c r="I30" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F31" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="G31" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="H31" s="3">
         <v>115</v>
       </c>
       <c r="I31" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F32" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="G32" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="H32" s="3">
         <v>355</v>
       </c>
       <c r="I32" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F33" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="G33" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="H33" s="3">
         <v>98</v>
       </c>
       <c r="I33" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F34" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="G34" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="H34" s="3">
         <v>145</v>
       </c>
       <c r="I34" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F35" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="G35" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="H35" s="3">
         <v>265</v>
       </c>
       <c r="I35" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="B36" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E36" t="s">
         <v>14</v>
       </c>
       <c r="F36" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="G36" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="H36" s="3">
         <v>290</v>
       </c>
       <c r="I36" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="E37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="G37" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="H37" s="3">
         <v>240</v>
       </c>
       <c r="I37" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -2357,13 +2312,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2374,15 +2329,15 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -2390,29 +2345,29 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/Bargaining_Tracker_Candidate_Dataset.xlsx
+++ b/src/data/Bargaining_Tracker_Candidate_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FEBA RACHEL JOHNY\Desktop\SkillSet\E tu\bargaining-tracker\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C932F9-0E36-4880-A897-53EAC91DC57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FF6F4E-E869-4F5D-A037-573683E0DFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="227">
   <si>
     <t>Employer Name</t>
   </si>
@@ -290,9 +290,6 @@
     <t>Metro Glass Tech</t>
   </si>
   <si>
-    <t>2026-10-10</t>
-  </si>
-  <si>
     <t>Ethan Clarke</t>
   </si>
   <si>
@@ -702,6 +699,9 @@
   </si>
   <si>
     <t>kiri.wallace@example.com</t>
+  </si>
+  <si>
+    <t>moana.teawa@example.com</t>
   </si>
 </sst>
 </file>
@@ -711,7 +711,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -724,6 +724,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -763,10 +771,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -776,8 +785,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1162,7 +1173,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H2" s="3">
         <v>320</v>
@@ -1194,7 +1205,7 @@
         <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H3" s="3">
         <v>140</v>
@@ -1226,7 +1237,7 @@
         <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H4" s="3">
         <v>260</v>
@@ -1258,7 +1269,7 @@
         <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H5" s="3">
         <v>410</v>
@@ -1290,7 +1301,7 @@
         <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H6" s="3">
         <v>95</v>
@@ -1322,7 +1333,7 @@
         <v>41</v>
       </c>
       <c r="G7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H7" s="3">
         <v>85</v>
@@ -1354,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H8" s="3">
         <v>180</v>
@@ -1386,7 +1397,7 @@
         <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H9" s="3">
         <v>230</v>
@@ -1418,7 +1429,7 @@
         <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H10" s="3">
         <v>120</v>
@@ -1450,7 +1461,7 @@
         <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H11" s="3">
         <v>510</v>
@@ -1482,7 +1493,7 @@
         <v>66</v>
       </c>
       <c r="G12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H12" s="3">
         <v>70</v>
@@ -1514,7 +1525,7 @@
         <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H13" s="3">
         <v>160</v>
@@ -1546,7 +1557,7 @@
         <v>77</v>
       </c>
       <c r="G14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H14" s="3">
         <v>460</v>
@@ -1577,8 +1588,8 @@
       <c r="F15" t="s">
         <v>81</v>
       </c>
-      <c r="G15" t="s">
-        <v>18</v>
+      <c r="G15" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="H15" s="3">
         <v>210</v>
@@ -1610,7 +1621,7 @@
         <v>85</v>
       </c>
       <c r="G16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H16" s="3">
         <v>175</v>
@@ -1632,31 +1643,31 @@
       <c r="C17" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>89</v>
+      <c r="D17" s="2">
+        <v>47401</v>
       </c>
       <c r="E17" t="s">
         <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H17" s="3">
         <v>390</v>
       </c>
       <c r="I17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s">
         <v>75</v>
@@ -1665,30 +1676,30 @@
         <v>19</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
         <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H18" s="3">
         <v>145</v>
       </c>
       <c r="I18" t="s">
+        <v>95</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B19" t="s">
         <v>75</v>
@@ -1697,65 +1708,65 @@
         <v>30</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E19" t="s">
         <v>20</v>
       </c>
       <c r="F19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H19" s="3">
         <v>620</v>
       </c>
       <c r="I19" t="s">
+        <v>100</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s">
         <v>103</v>
-      </c>
-      <c r="B20" t="s">
-        <v>104</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
         <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H20" s="3">
         <v>980</v>
       </c>
       <c r="I20" t="s">
+        <v>106</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
         <v>25</v>
@@ -1767,59 +1778,59 @@
         <v>20</v>
       </c>
       <c r="F21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H21" s="3">
         <v>340</v>
       </c>
       <c r="I21" t="s">
+        <v>110</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E22" t="s">
         <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H22" s="3">
         <v>275</v>
       </c>
       <c r="I22" t="s">
+        <v>115</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
         <v>30</v>
@@ -1831,91 +1842,91 @@
         <v>20</v>
       </c>
       <c r="F23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H23" s="3">
         <v>540</v>
       </c>
       <c r="I23" t="s">
+        <v>119</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
         <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H24" s="3">
         <v>190</v>
       </c>
       <c r="I24" t="s">
+        <v>124</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E25" t="s">
         <v>20</v>
       </c>
       <c r="F25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G25" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H25" s="3">
         <v>430</v>
       </c>
       <c r="I25" t="s">
+        <v>129</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
         <v>132</v>
-      </c>
-      <c r="B26" t="s">
-        <v>133</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -1927,27 +1938,27 @@
         <v>14</v>
       </c>
       <c r="F26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H26" s="3">
         <v>220</v>
       </c>
       <c r="I26" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C27" t="s">
         <v>25</v>
@@ -1959,27 +1970,27 @@
         <v>20</v>
       </c>
       <c r="F27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H27" s="3">
         <v>310</v>
       </c>
       <c r="I27" t="s">
+        <v>138</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
         <v>19</v>
@@ -1991,27 +2002,27 @@
         <v>20</v>
       </c>
       <c r="F28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H28" s="3">
         <v>130</v>
       </c>
       <c r="I28" t="s">
+        <v>142</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
         <v>30</v>
@@ -2023,88 +2034,88 @@
         <v>35</v>
       </c>
       <c r="F29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H29" s="3">
         <v>205</v>
       </c>
       <c r="I29" t="s">
+        <v>146</v>
+      </c>
+      <c r="J29" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E30" t="s">
         <v>20</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H30" s="3">
         <v>155</v>
       </c>
       <c r="I30" t="s">
+        <v>151</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s">
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E31" t="s">
         <v>20</v>
       </c>
       <c r="F31" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H31" s="3">
         <v>115</v>
       </c>
       <c r="I31" t="s">
+        <v>156</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B32" t="s">
         <v>75</v>
@@ -2113,30 +2124,30 @@
         <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E32" t="s">
         <v>20</v>
       </c>
       <c r="F32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H32" s="3">
         <v>355</v>
       </c>
       <c r="I32" t="s">
+        <v>161</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
@@ -2145,30 +2156,30 @@
         <v>30</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E33" t="s">
         <v>20</v>
       </c>
       <c r="F33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H33" s="3">
         <v>98</v>
       </c>
       <c r="I33" t="s">
+        <v>166</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B34" t="s">
         <v>45</v>
@@ -2177,94 +2188,94 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E34" t="s">
         <v>20</v>
       </c>
       <c r="F34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G34" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H34" s="3">
         <v>145</v>
       </c>
       <c r="I34" t="s">
+        <v>171</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E35" t="s">
         <v>20</v>
       </c>
       <c r="F35" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H35" s="3">
         <v>265</v>
       </c>
       <c r="I35" t="s">
+        <v>176</v>
+      </c>
+      <c r="J35" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C36" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E36" t="s">
         <v>14</v>
       </c>
       <c r="F36" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H36" s="3">
         <v>290</v>
       </c>
       <c r="I36" t="s">
+        <v>181</v>
+      </c>
+      <c r="J36" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B37" t="s">
         <v>75</v>
@@ -2273,31 +2284,34 @@
         <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E37" t="s">
         <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H37" s="3">
         <v>240</v>
       </c>
       <c r="I37" t="s">
+        <v>186</v>
+      </c>
+      <c r="J37" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="J37" s="2" t="s">
-        <v>188</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G15" r:id="rId1" xr:uid="{D7AA0AD6-680A-492A-A3D9-6A07AB443BCA}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2312,13 +2326,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2356,7 +2370,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
@@ -2367,7 +2381,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
